--- a/data/processed/Scenarios.xlsx
+++ b/data/processed/Scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WHO-CVD/github/uw-who-cvdtargets/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="465" documentId="8_{37DD4D6C-A1E8-49CB-B96F-22A9EB69CDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDF39131-31DF-4FB1-A25A-02EC87818D60}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="8_{37DD4D6C-A1E8-49CB-B96F-22A9EB69CDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C152163E-694B-4392-AA09-A49032E62292}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E9BE896-48AB-4A3E-A255-F19187E5388A}"/>
   </bookViews>
@@ -3861,11 +3861,11 @@
         <v>1</v>
       </c>
       <c r="V10" s="15">
-        <f t="shared" ref="V10:V41" si="2">+E10*B10*N10*O10</f>
+        <f>+E10*B10*N10*O10</f>
         <v>153684.49804897755</v>
       </c>
       <c r="W10" s="15">
-        <f t="shared" ref="W10:W41" si="3">+E10*B10*N10*0.8</f>
+        <f>+E10*B10*N10*0.8</f>
         <v>397108.50062585378</v>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
         <v>1033808.895840105</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" ref="G11:G41" si="4">+F11*C11</f>
+        <f t="shared" ref="G11:G41" si="2">+F11*C11</f>
         <v>111178.72428385183</v>
       </c>
       <c r="H11" s="4">
@@ -3900,23 +3900,23 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" ref="I11:I74" si="5">+F11*H11</f>
+        <f t="shared" ref="I11:I74" si="3">+F11*H11</f>
         <v>516904.44792005251</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" ref="J11:J41" si="6">C11+($K$5-$G$5)</f>
+        <f t="shared" ref="J11:J41" si="4">C11+($K$5-$G$5)</f>
         <v>0.15519871457927209</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" ref="K11:K74" si="7">+J11*F11</f>
+        <f t="shared" ref="K11:K74" si="5">+J11*F11</f>
         <v>160445.81175500088</v>
       </c>
       <c r="L11" s="9">
-        <f t="shared" ref="L11:L41" si="8">C11+($M$5-$G$5)</f>
+        <f t="shared" ref="L11:L41" si="6">C11+($M$5-$G$5)</f>
         <v>0.13758675364067358</v>
       </c>
       <c r="M11" s="2">
-        <f t="shared" ref="M11:M74" si="9">+F11*L11</f>
+        <f t="shared" ref="M11:M74" si="7">+F11*L11</f>
         <v>142238.4098634893</v>
       </c>
       <c r="N11" s="34">
@@ -3924,7 +3924,7 @@
         <v>6.1050695008231799E-2</v>
       </c>
       <c r="O11">
-        <f t="shared" ref="O11:O41" si="10">+C11+0.15</f>
+        <f t="shared" ref="O11:O41" si="8">+C11+0.15</f>
         <v>0.257542820274829</v>
       </c>
       <c r="P11" s="16">
@@ -3944,15 +3944,15 @@
         <v>0.10754282027482991</v>
       </c>
       <c r="U11">
-        <f t="shared" ref="U11:U74" si="11">IF(T11&gt;C11,1,0)</f>
+        <f t="shared" ref="U11:U74" si="9">IF(T11&gt;C11,1,0)</f>
         <v>1</v>
       </c>
       <c r="V11" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="V10:V41" si="10">+E11*B11*N11*O11</f>
         <v>16254.751127167401</v>
       </c>
       <c r="W11" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W10:W41" si="11">+E11*B11*N11*0.8</f>
         <v>50491.801277384904</v>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
         <v>10350758.734599421</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1796729.0272225791</v>
       </c>
       <c r="H12" s="4">
@@ -3987,23 +3987,23 @@
         <v>0.5</v>
       </c>
       <c r="I12" s="1">
+        <f t="shared" si="3"/>
+        <v>5175379.3672997104</v>
+      </c>
+      <c r="J12" s="9">
+        <f t="shared" si="4"/>
+        <v>0.22124017670266607</v>
+      </c>
+      <c r="K12" s="2">
         <f t="shared" si="5"/>
-        <v>5175379.3672997104</v>
-      </c>
-      <c r="J12" s="9">
+        <v>2290003.6914494401</v>
+      </c>
+      <c r="L12" s="9">
         <f t="shared" si="6"/>
-        <v>0.22124017670266607</v>
-      </c>
-      <c r="K12" s="2">
+        <v>0.20362821576406756</v>
+      </c>
+      <c r="M12" s="2">
         <f t="shared" si="7"/>
-        <v>2290003.6914494401</v>
-      </c>
-      <c r="L12" s="9">
-        <f t="shared" si="8"/>
-        <v>0.20362821576406756</v>
-      </c>
-      <c r="M12" s="2">
-        <f t="shared" si="9"/>
         <v>2107706.5329308179</v>
       </c>
       <c r="N12" s="34">
@@ -4011,7 +4011,7 @@
         <v>0.11948162384034801</v>
       </c>
       <c r="O12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.32358428239822301</v>
       </c>
       <c r="P12" s="16">
@@ -4031,15 +4031,15 @@
         <v>0.1735842823982239</v>
       </c>
       <c r="U12">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="10"/>
+        <v>400184.9210120833</v>
+      </c>
+      <c r="W12" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V12" s="15">
-        <f t="shared" si="2"/>
-        <v>400184.9210120833</v>
-      </c>
-      <c r="W12" s="15">
-        <f t="shared" si="3"/>
         <v>989380.36927168374</v>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
         <v>14946.003563304232</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1458.3832952128548</v>
       </c>
       <c r="H13" s="4">
@@ -4074,23 +4074,23 @@
         <v>0.5</v>
       </c>
       <c r="I13" s="1">
+        <f t="shared" si="3"/>
+        <v>7473.0017816521158</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="4"/>
+        <v>0.1452327006417245</v>
+      </c>
+      <c r="K13" s="2">
         <f t="shared" si="5"/>
-        <v>7473.0017816521158</v>
-      </c>
-      <c r="J13" s="9">
+        <v>2170.6484612995109</v>
+      </c>
+      <c r="L13" s="9">
         <f t="shared" si="6"/>
-        <v>0.1452327006417245</v>
-      </c>
-      <c r="K13" s="2">
+        <v>0.12762073970312598</v>
+      </c>
+      <c r="M13" s="2">
         <f t="shared" si="7"/>
-        <v>2170.6484612995109</v>
-      </c>
-      <c r="L13" s="9">
-        <f t="shared" si="8"/>
-        <v>0.12762073970312598</v>
-      </c>
-      <c r="M13" s="2">
-        <f t="shared" si="9"/>
         <v>1907.4200303544428</v>
       </c>
       <c r="N13" s="34">
@@ -4098,7 +4098,7 @@
         <v>0.187030251409458</v>
       </c>
       <c r="O13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.24757680633728141</v>
       </c>
       <c r="P13" s="16">
@@ -4118,15 +4118,15 @@
         <v>0.12762073970312598</v>
       </c>
       <c r="U13">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="10"/>
+        <v>692.06501495673092</v>
+      </c>
+      <c r="W13" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V13" s="15">
-        <f t="shared" si="2"/>
-        <v>692.06501495673092</v>
-      </c>
-      <c r="W13" s="15">
-        <f t="shared" si="3"/>
         <v>2236.2838432091567</v>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
         <v>25620.321136800001</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9654.4852956184423</v>
       </c>
       <c r="H14" s="4">
@@ -4161,23 +4161,23 @@
         <v>0.5</v>
       </c>
       <c r="I14" s="1">
+        <f t="shared" si="3"/>
+        <v>12810.160568400001</v>
+      </c>
+      <c r="J14" s="9">
+        <f t="shared" si="4"/>
+        <v>0.42448510124795513</v>
+      </c>
+      <c r="K14" s="2">
         <f t="shared" si="5"/>
-        <v>12810.160568400001</v>
-      </c>
-      <c r="J14" s="9">
+        <v>10875.444611759673</v>
+      </c>
+      <c r="L14" s="9">
         <f t="shared" si="6"/>
-        <v>0.42448510124795513</v>
-      </c>
-      <c r="K14" s="2">
+        <v>0.40687314030935662</v>
+      </c>
+      <c r="M14" s="2">
         <f t="shared" si="7"/>
-        <v>10875.444611759673</v>
-      </c>
-      <c r="L14" s="9">
-        <f t="shared" si="8"/>
-        <v>0.40687314030935662</v>
-      </c>
-      <c r="M14" s="2">
-        <f t="shared" si="9"/>
         <v>10424.220516664001</v>
       </c>
       <c r="N14" s="34">
@@ -4185,7 +4185,7 @@
         <v>5.8643140168872197E-2</v>
       </c>
       <c r="O14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.52682920694351199</v>
       </c>
       <c r="P14" s="16">
@@ -4205,15 +4205,15 @@
         <v>0.37682920694351202</v>
       </c>
       <c r="U14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="10"/>
+        <v>791.53774698880011</v>
+      </c>
+      <c r="W14" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="15">
-        <f t="shared" si="2"/>
-        <v>791.53774698880011</v>
-      </c>
-      <c r="W14" s="15">
-        <f t="shared" si="3"/>
         <v>1201.9648668775053</v>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
         <v>6359003.9130501896</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>867966.42184845801</v>
       </c>
       <c r="H15" s="4">
@@ -4248,23 +4248,23 @@
         <v>0.5</v>
       </c>
       <c r="I15" s="1">
+        <f t="shared" si="3"/>
+        <v>3179501.9565250948</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" si="4"/>
+        <v>0.18414997949712308</v>
+      </c>
+      <c r="K15" s="2">
         <f t="shared" si="5"/>
-        <v>3179501.9565250948</v>
-      </c>
-      <c r="J15" s="9">
+        <v>1171010.440210318</v>
+      </c>
+      <c r="L15" s="9">
         <f t="shared" si="6"/>
-        <v>0.18414997949712308</v>
-      </c>
-      <c r="K15" s="2">
+        <v>0.16653801855852457</v>
+      </c>
+      <c r="M15" s="2">
         <f t="shared" si="7"/>
-        <v>1171010.440210318</v>
-      </c>
-      <c r="L15" s="9">
-        <f t="shared" si="8"/>
-        <v>0.16653801855852457</v>
-      </c>
-      <c r="M15" s="2">
-        <f t="shared" si="9"/>
         <v>1059015.9116852828</v>
       </c>
       <c r="N15" s="34">
@@ -4272,7 +4272,7 @@
         <v>4.45450084697692E-2</v>
       </c>
       <c r="O15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.28649408519267999</v>
       </c>
       <c r="P15" s="16">
@@ -4292,15 +4292,15 @@
         <v>0.13649408519268039</v>
       </c>
       <c r="U15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="15">
+        <f t="shared" si="10"/>
+        <v>81152.854087632266</v>
+      </c>
+      <c r="W15" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="15">
-        <f t="shared" si="2"/>
-        <v>81152.854087632266</v>
-      </c>
-      <c r="W15" s="15">
-        <f t="shared" si="3"/>
         <v>226609.50653289296</v>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
         <v>33045.801145770005</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8420.3416787764381</v>
       </c>
       <c r="H16" s="4">
@@ -4335,23 +4335,23 @@
         <v>0.5</v>
       </c>
       <c r="I16" s="1">
+        <f t="shared" si="3"/>
+        <v>16522.900572885002</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="4"/>
+        <v>0.3024641115915061</v>
+      </c>
+      <c r="K16" s="2">
         <f t="shared" si="5"/>
-        <v>16522.900572885002</v>
-      </c>
-      <c r="J16" s="9">
+        <v>9995.1688853848991</v>
+      </c>
+      <c r="L16" s="9">
         <f t="shared" si="6"/>
-        <v>0.3024641115915061</v>
-      </c>
-      <c r="K16" s="2">
+        <v>0.28485215065290759</v>
+      </c>
+      <c r="M16" s="2">
         <f t="shared" si="7"/>
-        <v>9995.1688853848991</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="8"/>
-        <v>0.28485215065290759</v>
-      </c>
-      <c r="M16" s="2">
-        <f t="shared" si="9"/>
         <v>9413.1675264209043</v>
       </c>
       <c r="N16" s="34">
@@ -4359,7 +4359,7 @@
         <v>0.12481961002722</v>
       </c>
       <c r="O16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.40480821728706295</v>
       </c>
       <c r="P16" s="16">
@@ -4379,15 +4379,15 @@
         <v>0.2548082172870636</v>
       </c>
       <c r="U16">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" si="10"/>
+        <v>1669.7383664486326</v>
+      </c>
+      <c r="W16" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V16" s="15">
-        <f t="shared" si="2"/>
-        <v>1669.7383664486326</v>
-      </c>
-      <c r="W16" s="15">
-        <f t="shared" si="3"/>
         <v>3299.8112096416576</v>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
         <v>16943128.250510488</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2758860.3472550828</v>
       </c>
       <c r="H17" s="4">
@@ -4422,23 +4422,23 @@
         <v>0.5</v>
       </c>
       <c r="I17" s="1">
+        <f t="shared" si="3"/>
+        <v>8471564.1252552439</v>
+      </c>
+      <c r="J17" s="9">
+        <f t="shared" si="4"/>
+        <v>0.21048653020970809</v>
+      </c>
+      <c r="K17" s="2">
         <f t="shared" si="5"/>
-        <v>8471564.1252552439</v>
-      </c>
-      <c r="J17" s="9">
+        <v>3566300.2763480344</v>
+      </c>
+      <c r="L17" s="9">
         <f t="shared" si="6"/>
-        <v>0.21048653020970809</v>
-      </c>
-      <c r="K17" s="2">
+        <v>0.19287456927110957</v>
+      </c>
+      <c r="M17" s="2">
         <f t="shared" si="7"/>
-        <v>3566300.2763480344</v>
-      </c>
-      <c r="L17" s="9">
-        <f t="shared" si="8"/>
-        <v>0.19287456927110957</v>
-      </c>
-      <c r="M17" s="2">
-        <f t="shared" si="9"/>
         <v>3267898.5634223786</v>
       </c>
       <c r="N17" s="34">
@@ -4446,7 +4446,7 @@
         <v>5.1307119474561395E-2</v>
       </c>
       <c r="O17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.312830635905265</v>
       </c>
       <c r="P17" s="16">
@@ -4466,15 +4466,15 @@
         <v>0.16283063590526581</v>
       </c>
       <c r="U17">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="10"/>
+        <v>271944.6432635102</v>
+      </c>
+      <c r="W17" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V17" s="15">
-        <f t="shared" si="2"/>
-        <v>271944.6432635102</v>
-      </c>
-      <c r="W17" s="15">
-        <f t="shared" si="3"/>
         <v>695442.48433740647</v>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
         <v>1134211.1081533502</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>115856.47111364706</v>
       </c>
       <c r="H18" s="4">
@@ -4509,23 +4509,23 @@
         <v>0.5</v>
       </c>
       <c r="I18" s="1">
+        <f t="shared" si="3"/>
+        <v>567105.55407667509</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="4"/>
+        <v>0.1498030786167861</v>
+      </c>
+      <c r="K18" s="2">
         <f t="shared" si="5"/>
-        <v>567105.55407667509</v>
-      </c>
-      <c r="J18" s="9">
+        <v>169908.31580272841</v>
+      </c>
+      <c r="L18" s="9">
         <f t="shared" si="6"/>
-        <v>0.1498030786167861</v>
-      </c>
-      <c r="K18" s="2">
+        <v>0.13219111767818759</v>
+      </c>
+      <c r="M18" s="2">
         <f t="shared" si="7"/>
-        <v>169908.31580272841</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="8"/>
-        <v>0.13219111767818759</v>
-      </c>
-      <c r="M18" s="2">
-        <f t="shared" si="9"/>
         <v>149932.63406980707</v>
       </c>
       <c r="N18" s="34">
@@ -4533,7 +4533,7 @@
         <v>7.2854139721639802E-2</v>
       </c>
       <c r="O18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.25214718431234301</v>
       </c>
       <c r="P18" s="16">
@@ -4553,15 +4553,15 @@
         <v>0.1021471843123436</v>
       </c>
       <c r="U18">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="10"/>
+        <v>20835.419716255783</v>
+      </c>
+      <c r="W18" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V18" s="15">
-        <f t="shared" si="2"/>
-        <v>20835.419716255783</v>
-      </c>
-      <c r="W18" s="15">
-        <f t="shared" si="3"/>
         <v>66105.579637792063</v>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
         <v>7107748.9135027202</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2013944.5789054292</v>
       </c>
       <c r="H19" s="4">
@@ -4596,23 +4596,23 @@
         <v>0.5</v>
       </c>
       <c r="I19" s="1">
+        <f t="shared" si="3"/>
+        <v>3553874.4567513601</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="4"/>
+        <v>0.33100081875436305</v>
+      </c>
+      <c r="K19" s="2">
         <f t="shared" si="5"/>
-        <v>3553874.4567513601</v>
-      </c>
-      <c r="J19" s="9">
+        <v>2352670.7098698346</v>
+      </c>
+      <c r="L19" s="9">
         <f t="shared" si="6"/>
-        <v>0.33100081875436305</v>
-      </c>
-      <c r="K19" s="2">
+        <v>0.31338885781576453</v>
+      </c>
+      <c r="M19" s="2">
         <f t="shared" si="7"/>
-        <v>2352670.7098698346</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" si="8"/>
-        <v>0.31338885781576453</v>
-      </c>
-      <c r="M19" s="2">
-        <f t="shared" si="9"/>
         <v>2227489.3136438588</v>
       </c>
       <c r="N19" s="34">
@@ -4620,7 +4620,7 @@
         <v>4.52888402764038E-2</v>
       </c>
       <c r="O19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.43334492444992001</v>
       </c>
       <c r="P19" s="16">
@@ -4640,15 +4640,15 @@
         <v>0.28334492444992071</v>
       </c>
       <c r="U19">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V19" s="15">
+        <f t="shared" si="10"/>
+        <v>139494.47014983839</v>
+      </c>
+      <c r="W19" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V19" s="15">
-        <f t="shared" si="2"/>
-        <v>139494.47014983839</v>
-      </c>
-      <c r="W19" s="15">
-        <f t="shared" si="3"/>
         <v>257521.36421472591</v>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
         <v>2820230.6444839151</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>885479.66515313473</v>
       </c>
       <c r="H20" s="4">
@@ -4683,23 +4683,23 @@
         <v>0.5</v>
       </c>
       <c r="I20" s="1">
+        <f t="shared" si="3"/>
+        <v>1410115.3222419575</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="4"/>
+        <v>0.36163009598367213</v>
+      </c>
+      <c r="K20" s="2">
         <f t="shared" si="5"/>
-        <v>1410115.3222419575</v>
-      </c>
-      <c r="J20" s="9">
+        <v>1019880.2786608117</v>
+      </c>
+      <c r="L20" s="9">
         <f t="shared" si="6"/>
-        <v>0.36163009598367213</v>
-      </c>
-      <c r="K20" s="2">
+        <v>0.34401813504507361</v>
+      </c>
+      <c r="M20" s="2">
         <f t="shared" si="7"/>
-        <v>1019880.2786608117</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="8"/>
-        <v>0.34401813504507361</v>
-      </c>
-      <c r="M20" s="2">
-        <f t="shared" si="9"/>
         <v>970210.48671232245</v>
       </c>
       <c r="N20" s="34">
@@ -4707,7 +4707,7 @@
         <v>5.1667703462107001E-2</v>
       </c>
       <c r="O20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.46397420167922898</v>
       </c>
       <c r="P20" s="16">
@@ -4727,15 +4727,15 @@
         <v>0.31397420167922968</v>
       </c>
       <c r="U20">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V20" s="15">
+        <f t="shared" si="10"/>
+        <v>67607.926855949248</v>
+      </c>
+      <c r="W20" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V20" s="15">
-        <f t="shared" si="2"/>
-        <v>67607.926855949248</v>
-      </c>
-      <c r="W20" s="15">
-        <f t="shared" si="3"/>
         <v>116571.87250715349</v>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
         <v>3174577.4404234798</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>470796.71580040659</v>
       </c>
       <c r="H21" s="4">
@@ -4770,23 +4770,23 @@
         <v>0.5</v>
       </c>
       <c r="I21" s="1">
+        <f t="shared" si="3"/>
+        <v>1587288.7202117399</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="4"/>
+        <v>0.19595806195848009</v>
+      </c>
+      <c r="K21" s="2">
         <f t="shared" si="5"/>
-        <v>1587288.7202117399</v>
-      </c>
-      <c r="J21" s="9">
+        <v>622084.04276249744</v>
+      </c>
+      <c r="L21" s="9">
         <f t="shared" si="6"/>
-        <v>0.19595806195848009</v>
-      </c>
-      <c r="K21" s="2">
+        <v>0.17834610101988158</v>
+      </c>
+      <c r="M21" s="2">
         <f t="shared" si="7"/>
-        <v>622084.04276249744</v>
-      </c>
-      <c r="L21" s="9">
-        <f t="shared" si="8"/>
-        <v>0.17834610101988158</v>
-      </c>
-      <c r="M21" s="2">
-        <f t="shared" si="9"/>
         <v>566173.50888520305</v>
       </c>
       <c r="N21" s="34">
@@ -4794,7 +4794,7 @@
         <v>6.7644852413161094E-2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.298302167654037</v>
       </c>
       <c r="P21" s="16">
@@ -4814,15 +4814,15 @@
         <v>0.1483021676540375</v>
       </c>
       <c r="U21">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V21" s="15">
+        <f t="shared" si="10"/>
+        <v>64058.547721658993</v>
+      </c>
+      <c r="W21" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V21" s="15">
-        <f t="shared" si="2"/>
-        <v>64058.547721658993</v>
-      </c>
-      <c r="W21" s="15">
-        <f t="shared" si="3"/>
         <v>171795.0579452776</v>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>144759.91458809999</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>35827.246568632108</v>
       </c>
       <c r="H22" s="4">
@@ -4857,23 +4857,23 @@
         <v>0.5</v>
       </c>
       <c r="I22" s="1">
+        <f t="shared" si="3"/>
+        <v>72379.957294049993</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="4"/>
+        <v>0.29515014484040808</v>
+      </c>
+      <c r="K22" s="2">
         <f t="shared" si="5"/>
-        <v>72379.957294049993</v>
-      </c>
-      <c r="J22" s="9">
+        <v>42725.909757762813</v>
+      </c>
+      <c r="L22" s="9">
         <f t="shared" si="6"/>
-        <v>0.29515014484040808</v>
-      </c>
-      <c r="K22" s="2">
+        <v>0.27753818390180957</v>
+      </c>
+      <c r="M22" s="2">
         <f t="shared" si="7"/>
-        <v>42725.909757762813</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" si="8"/>
-        <v>0.27753818390180957</v>
-      </c>
-      <c r="M22" s="2">
-        <f t="shared" si="9"/>
         <v>40176.403796562336</v>
       </c>
       <c r="N22" s="34">
@@ -4881,7 +4881,7 @@
         <v>0.11177245649170199</v>
       </c>
       <c r="O22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.39749425053596499</v>
       </c>
       <c r="P22" s="16">
@@ -4901,15 +4901,15 @@
         <v>0.24749425053596499</v>
       </c>
       <c r="U22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="15">
+        <f t="shared" si="10"/>
+        <v>6431.5250465660474</v>
+      </c>
+      <c r="W22" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="15">
-        <f t="shared" si="2"/>
-        <v>6431.5250465660474</v>
-      </c>
-      <c r="W22" s="15">
-        <f t="shared" si="3"/>
         <v>12944.137004032722</v>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
         <v>405442.46502294001</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>74053.437855833981</v>
       </c>
       <c r="H23" s="4">
@@ -4944,23 +4944,23 @@
         <v>0.5</v>
       </c>
       <c r="I23" s="1">
+        <f t="shared" si="3"/>
+        <v>202721.23251147001</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="4"/>
+        <v>0.23030434444062708</v>
+      </c>
+      <c r="K23" s="2">
         <f t="shared" si="5"/>
-        <v>202721.23251147001</v>
-      </c>
-      <c r="J23" s="9">
+        <v>93375.161115500072</v>
+      </c>
+      <c r="L23" s="9">
         <f t="shared" si="6"/>
-        <v>0.23030434444062708</v>
-      </c>
-      <c r="K23" s="2">
+        <v>0.21269238350202857</v>
+      </c>
+      <c r="M23" s="2">
         <f t="shared" si="7"/>
-        <v>93375.161115500072</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="8"/>
-        <v>0.21269238350202857</v>
-      </c>
-      <c r="M23" s="2">
-        <f t="shared" si="9"/>
         <v>86234.524258666963</v>
       </c>
       <c r="N23" s="34">
@@ -4968,7 +4968,7 @@
         <v>0.21294375543612401</v>
       </c>
       <c r="O23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.33264845013618399</v>
       </c>
       <c r="P23" s="16">
@@ -4988,15 +4988,15 @@
         <v>0.18264845013618469</v>
       </c>
       <c r="U23">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V23" s="15">
+        <f t="shared" si="10"/>
+        <v>28719.68332726655</v>
+      </c>
+      <c r="W23" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V23" s="15">
-        <f t="shared" si="2"/>
-        <v>28719.68332726655</v>
-      </c>
-      <c r="W23" s="15">
-        <f t="shared" si="3"/>
         <v>69069.152892211365</v>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
         <v>32124468.764312673</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5062727.256648683</v>
       </c>
       <c r="H24" s="4">
@@ -5031,23 +5031,23 @@
         <v>0.5</v>
       </c>
       <c r="I24" s="1">
+        <f t="shared" si="3"/>
+        <v>16062234.382156337</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="4"/>
+        <v>0.20525312318914007</v>
+      </c>
+      <c r="K24" s="2">
         <f t="shared" si="5"/>
-        <v>16062234.382156337</v>
-      </c>
-      <c r="J24" s="9">
+        <v>6593647.5446671518</v>
+      </c>
+      <c r="L24" s="9">
         <f t="shared" si="6"/>
-        <v>0.20525312318914007</v>
-      </c>
-      <c r="K24" s="2">
+        <v>0.18764116225054156</v>
+      </c>
+      <c r="M24" s="2">
         <f t="shared" si="7"/>
-        <v>6593647.5446671518</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" si="8"/>
-        <v>0.18764116225054156</v>
-      </c>
-      <c r="M24" s="2">
-        <f t="shared" si="9"/>
         <v>6027872.6556168487</v>
       </c>
       <c r="N24" s="34">
@@ -5055,7 +5055,7 @@
         <v>6.4803578145428406E-2</v>
       </c>
       <c r="O24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.30759722888469698</v>
       </c>
       <c r="P24" s="16">
@@ -5075,15 +5075,15 @@
         <v>0.15759722888469699</v>
       </c>
       <c r="U24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="15">
+        <f t="shared" si="10"/>
+        <v>640349.91969749983</v>
+      </c>
+      <c r="W24" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="15">
-        <f t="shared" si="2"/>
-        <v>640349.91969749983</v>
-      </c>
-      <c r="W24" s="15">
-        <f t="shared" si="3"/>
         <v>1665424.4175588083</v>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
         <v>108341.3350502</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>40992.996526874929</v>
       </c>
       <c r="H25" s="4">
@@ -5118,23 +5118,23 @@
         <v>0.5</v>
       </c>
       <c r="I25" s="1">
+        <f t="shared" si="3"/>
+        <v>54170.667525099998</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="4"/>
+        <v>0.42602483823411508</v>
+      </c>
+      <c r="K25" s="2">
         <f t="shared" si="5"/>
-        <v>54170.667525099998</v>
-      </c>
-      <c r="J25" s="9">
+        <v>46156.099738829515</v>
+      </c>
+      <c r="L25" s="9">
         <f t="shared" si="6"/>
-        <v>0.42602483823411508</v>
-      </c>
-      <c r="K25" s="2">
+        <v>0.40841287729551656</v>
+      </c>
+      <c r="M25" s="2">
         <f t="shared" si="7"/>
-        <v>46156.099738829515</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="8"/>
-        <v>0.40841287729551656</v>
-      </c>
-      <c r="M25" s="2">
-        <f t="shared" si="9"/>
         <v>44247.99637788978</v>
       </c>
       <c r="N25" s="34">
@@ -5142,7 +5142,7 @@
         <v>0.18393577000314398</v>
       </c>
       <c r="O25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.52836894392967204</v>
       </c>
       <c r="P25" s="16">
@@ -5162,15 +5162,15 @@
         <v>0.37836894392967219</v>
       </c>
       <c r="U25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="15">
+        <f t="shared" si="10"/>
+        <v>10529.25541375102</v>
+      </c>
+      <c r="W25" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="15">
-        <f t="shared" si="2"/>
-        <v>10529.25541375102</v>
-      </c>
-      <c r="W25" s="15">
-        <f t="shared" si="3"/>
         <v>15942.277508501718</v>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
         <v>3861762.5067308098</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>470824.34703375219</v>
       </c>
       <c r="H26" s="4">
@@ -5205,23 +5205,23 @@
         <v>0.5</v>
       </c>
       <c r="I26" s="1">
+        <f t="shared" si="3"/>
+        <v>1930881.2533654049</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="4"/>
+        <v>0.16957544430606408</v>
+      </c>
+      <c r="K26" s="2">
         <f t="shared" si="5"/>
-        <v>1930881.2533654049</v>
-      </c>
-      <c r="J26" s="9">
+        <v>654860.09288337687</v>
+      </c>
+      <c r="L26" s="9">
         <f t="shared" si="6"/>
-        <v>0.16957544430606408</v>
-      </c>
-      <c r="K26" s="2">
+        <v>0.15196348336746557</v>
+      </c>
+      <c r="M26" s="2">
         <f t="shared" si="7"/>
-        <v>654860.09288337687</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" si="8"/>
-        <v>0.15196348336746557</v>
-      </c>
-      <c r="M26" s="2">
-        <f t="shared" si="9"/>
         <v>586846.88246068952</v>
       </c>
       <c r="N26" s="34">
@@ -5229,7 +5229,7 @@
         <v>7.09609662162871E-2</v>
       </c>
       <c r="O26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.27191955000162099</v>
       </c>
       <c r="P26" s="16">
@@ -5249,15 +5249,15 @@
         <v>0.1219195500016212</v>
       </c>
       <c r="U26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="15">
+        <f t="shared" si="10"/>
+        <v>74515.310399984897</v>
+      </c>
+      <c r="W26" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="15">
-        <f t="shared" si="2"/>
-        <v>74515.310399984897</v>
-      </c>
-      <c r="W26" s="15">
-        <f t="shared" si="3"/>
         <v>219227.51902035938</v>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
         <v>3280759.8885189253</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1404971.3912602665</v>
       </c>
       <c r="H27" s="4">
@@ -5292,23 +5292,23 @@
         <v>0.5</v>
       </c>
       <c r="I27" s="1">
+        <f t="shared" si="3"/>
+        <v>1640379.9442594626</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="4"/>
+        <v>0.47590161755197113</v>
+      </c>
+      <c r="K27" s="2">
         <f t="shared" si="5"/>
-        <v>1640379.9442594626</v>
-      </c>
-      <c r="J27" s="9">
+        <v>1561318.9377457811</v>
+      </c>
+      <c r="L27" s="9">
         <f t="shared" si="6"/>
-        <v>0.47590161755197113</v>
-      </c>
-      <c r="K27" s="2">
+        <v>0.45828965661337262</v>
+      </c>
+      <c r="M27" s="2">
         <f t="shared" si="7"/>
-        <v>1561318.9377457811</v>
-      </c>
-      <c r="L27" s="9">
-        <f t="shared" si="8"/>
-        <v>0.45828965661337262</v>
-      </c>
-      <c r="M27" s="2">
-        <f t="shared" si="9"/>
         <v>1503538.3227402649</v>
       </c>
       <c r="N27" s="34">
@@ -5316,7 +5316,7 @@
         <v>6.35195062337401E-2</v>
       </c>
       <c r="O27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.57824572324752799</v>
       </c>
       <c r="P27" s="16">
@@ -5336,15 +5336,15 @@
         <v>0.42824572324752808</v>
       </c>
       <c r="U27">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="15">
+        <f t="shared" si="10"/>
+        <v>120501.92627391034</v>
+      </c>
+      <c r="W27" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="15">
-        <f t="shared" si="2"/>
-        <v>120501.92627391034</v>
-      </c>
-      <c r="W27" s="15">
-        <f t="shared" si="3"/>
         <v>166713.79855214589</v>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         <v>104309.85383357</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23919.50614264101</v>
       </c>
       <c r="H28" s="4">
@@ -5379,23 +5379,23 @@
         <v>0.5</v>
       </c>
       <c r="I28" s="1">
+        <f t="shared" si="3"/>
+        <v>52154.926916785</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="4"/>
+        <v>0.27696794166677008</v>
+      </c>
+      <c r="K28" s="2">
         <f t="shared" si="5"/>
-        <v>52154.926916785</v>
-      </c>
-      <c r="J28" s="9">
+        <v>28890.485511845531</v>
+      </c>
+      <c r="L28" s="9">
         <f t="shared" si="6"/>
-        <v>0.27696794166677008</v>
-      </c>
-      <c r="K28" s="2">
+        <v>0.25935598072817156</v>
+      </c>
+      <c r="M28" s="2">
         <f t="shared" si="7"/>
-        <v>28890.485511845531</v>
-      </c>
-      <c r="L28" s="9">
-        <f t="shared" si="8"/>
-        <v>0.25935598072817156</v>
-      </c>
-      <c r="M28" s="2">
-        <f t="shared" si="9"/>
         <v>27053.384440617774</v>
       </c>
       <c r="N28" s="34">
@@ -5403,7 +5403,7 @@
         <v>9.4762519512879492E-2</v>
       </c>
       <c r="O28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.37931204736232699</v>
       </c>
       <c r="P28" s="16">
@@ -5423,15 +5423,15 @@
         <v>0.2293120473623276</v>
       </c>
       <c r="U28">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V28" s="15">
+        <f t="shared" si="10"/>
+        <v>3749.3723514738526</v>
+      </c>
+      <c r="W28" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V28" s="15">
-        <f t="shared" si="2"/>
-        <v>3749.3723514738526</v>
-      </c>
-      <c r="W28" s="15">
-        <f t="shared" si="3"/>
         <v>7907.7316474314284</v>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
         <v>1922216.90626728</v>
       </c>
       <c r="G29" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>210117.14552148315</v>
       </c>
       <c r="H29" s="4">
@@ -5466,23 +5466,23 @@
         <v>0.5</v>
       </c>
       <c r="I29" s="1">
+        <f t="shared" si="3"/>
+        <v>961108.45313364</v>
+      </c>
+      <c r="J29" s="9">
+        <f t="shared" si="4"/>
+        <v>0.1569656942736391</v>
+      </c>
+      <c r="K29" s="2">
         <f t="shared" si="5"/>
-        <v>961108.45313364</v>
-      </c>
-      <c r="J29" s="9">
+        <v>301722.11123677023</v>
+      </c>
+      <c r="L29" s="9">
         <f t="shared" si="6"/>
-        <v>0.1569656942736391</v>
-      </c>
-      <c r="K29" s="2">
+        <v>0.13935373333504059</v>
+      </c>
+      <c r="M29" s="2">
         <f t="shared" si="7"/>
-        <v>301722.11123677023</v>
-      </c>
-      <c r="L29" s="9">
-        <f t="shared" si="8"/>
-        <v>0.13935373333504059</v>
-      </c>
-      <c r="M29" s="2">
-        <f t="shared" si="9"/>
         <v>267868.10216807725</v>
       </c>
       <c r="N29" s="34">
@@ -5490,7 +5490,7 @@
         <v>2.8842594379886E-2</v>
       </c>
       <c r="O29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.25930979996919601</v>
       </c>
       <c r="P29" s="16">
@@ -5510,15 +5510,15 @@
         <v>0.10930979996919631</v>
       </c>
       <c r="U29">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="15">
+        <f t="shared" si="10"/>
+        <v>14376.581981179595</v>
+      </c>
+      <c r="W29" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="15">
-        <f t="shared" si="2"/>
-        <v>14376.581981179595</v>
-      </c>
-      <c r="W29" s="15">
-        <f t="shared" si="3"/>
         <v>44353.378030101208</v>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
         <v>22331.84809439343</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>4319.4120141028834</v>
       </c>
       <c r="H30" s="4">
@@ -5553,23 +5553,23 @@
         <v>0.5</v>
       </c>
       <c r="I30" s="1">
+        <f t="shared" si="3"/>
+        <v>11165.924047196715</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="4"/>
+        <v>0.24107526541270807</v>
+      </c>
+      <c r="K30" s="2">
         <f t="shared" si="5"/>
-        <v>11165.924047196715</v>
-      </c>
-      <c r="J30" s="9">
+        <v>5383.6562065121752</v>
+      </c>
+      <c r="L30" s="9">
         <f t="shared" si="6"/>
-        <v>0.24107526541270807</v>
-      </c>
-      <c r="K30" s="2">
+        <v>0.22346330447410956</v>
+      </c>
+      <c r="M30" s="2">
         <f t="shared" si="7"/>
-        <v>5383.6562065121752</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" si="8"/>
-        <v>0.22346330447410956</v>
-      </c>
-      <c r="M30" s="2">
-        <f t="shared" si="9"/>
         <v>4990.3485701870022</v>
       </c>
       <c r="N30" s="34">
@@ -5577,7 +5577,7 @@
         <v>0.10871430142479699</v>
       </c>
       <c r="O30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.34341937110826498</v>
       </c>
       <c r="P30" s="16">
@@ -5597,15 +5597,15 @@
         <v>0.22346330447410956</v>
       </c>
       <c r="U30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V30" s="15">
+        <f t="shared" si="10"/>
+        <v>833.75054944507008</v>
+      </c>
+      <c r="W30" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V30" s="15">
-        <f t="shared" si="2"/>
-        <v>833.75054944507008</v>
-      </c>
-      <c r="W30" s="15">
-        <f t="shared" si="3"/>
         <v>1942.2330120853323</v>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
         <v>246997.777906</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>22542.430806967863</v>
       </c>
       <c r="H31" s="4">
@@ -5640,23 +5640,23 @@
         <v>0.5</v>
       </c>
       <c r="I31" s="1">
+        <f t="shared" si="3"/>
+        <v>123498.888953</v>
+      </c>
+      <c r="J31" s="9">
+        <f t="shared" si="4"/>
+        <v>0.13892161741368839</v>
+      </c>
+      <c r="K31" s="2">
         <f t="shared" si="5"/>
-        <v>123498.888953</v>
-      </c>
-      <c r="J31" s="9">
+        <v>34313.330804288504</v>
+      </c>
+      <c r="L31" s="9">
         <f t="shared" si="6"/>
-        <v>0.13892161741368839</v>
-      </c>
-      <c r="K31" s="2">
+        <v>0.12130965647508987</v>
+      </c>
+      <c r="M31" s="2">
         <f t="shared" si="7"/>
-        <v>34313.330804288504</v>
-      </c>
-      <c r="L31" s="9">
-        <f t="shared" si="8"/>
-        <v>0.12130965647508987</v>
-      </c>
-      <c r="M31" s="2">
-        <f t="shared" si="9"/>
         <v>29963.215587887404</v>
       </c>
       <c r="N31" s="34">
@@ -5664,7 +5664,7 @@
         <v>5.58595356661458E-2</v>
       </c>
       <c r="O31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.24126572310924529</v>
       </c>
       <c r="P31" s="16">
@@ -5684,15 +5684,15 @@
         <v>9.12657231092453E-2</v>
       </c>
       <c r="U31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="15">
+        <f t="shared" si="10"/>
+        <v>3328.7868953232901</v>
+      </c>
+      <c r="W31" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V31" s="15">
-        <f t="shared" si="2"/>
-        <v>3328.7868953232901</v>
-      </c>
-      <c r="W31" s="15">
-        <f t="shared" si="3"/>
         <v>11037.744947519175</v>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
         <v>2253327.10283024</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>642486.37569594686</v>
       </c>
       <c r="H32" s="4">
@@ -5727,23 +5727,23 @@
         <v>0.5</v>
       </c>
       <c r="I32" s="1">
+        <f t="shared" si="3"/>
+        <v>1126663.55141512</v>
+      </c>
+      <c r="J32" s="9">
+        <f t="shared" si="4"/>
+        <v>0.33278377249352908</v>
+      </c>
+      <c r="K32" s="2">
         <f t="shared" si="5"/>
-        <v>1126663.55141512</v>
-      </c>
-      <c r="J32" s="9">
+        <v>749870.69394176162</v>
+      </c>
+      <c r="L32" s="9">
         <f t="shared" si="6"/>
-        <v>0.33278377249352908</v>
-      </c>
-      <c r="K32" s="2">
+        <v>0.31517181155493057</v>
+      </c>
+      <c r="M32" s="2">
         <f t="shared" si="7"/>
-        <v>749870.69394176162</v>
-      </c>
-      <c r="L32" s="9">
-        <f t="shared" si="8"/>
-        <v>0.31517181155493057</v>
-      </c>
-      <c r="M32" s="2">
-        <f t="shared" si="9"/>
         <v>710185.18502483005</v>
       </c>
       <c r="N32" s="34">
@@ -5751,7 +5751,7 @@
         <v>5.2394093773273497E-2</v>
       </c>
       <c r="O32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.43512787818908605</v>
       </c>
       <c r="P32" s="16">
@@ -5771,15 +5771,15 @@
         <v>0.28512787818908691</v>
       </c>
       <c r="U32">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V32" s="15">
+        <f t="shared" si="10"/>
+        <v>51371.646145396007</v>
+      </c>
+      <c r="W32" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V32" s="15">
-        <f t="shared" si="2"/>
-        <v>51371.646145396007</v>
-      </c>
-      <c r="W32" s="15">
-        <f t="shared" si="3"/>
         <v>94448.825222037034</v>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
         <v>1377869.6775780602</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>282294.3453106581</v>
       </c>
       <c r="H33" s="4">
@@ -5814,23 +5814,23 @@
         <v>0.5</v>
       </c>
       <c r="I33" s="1">
+        <f t="shared" si="3"/>
+        <v>688934.83878903009</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="4"/>
+        <v>0.25253328576200007</v>
+      </c>
+      <c r="K33" s="2">
         <f t="shared" si="5"/>
-        <v>688934.83878903009</v>
-      </c>
-      <c r="J33" s="9">
+        <v>347957.95703061519</v>
+      </c>
+      <c r="L33" s="9">
         <f t="shared" si="6"/>
-        <v>0.25253328576200007</v>
-      </c>
-      <c r="K33" s="2">
+        <v>0.23492132482340158</v>
+      </c>
+      <c r="M33" s="2">
         <f t="shared" si="7"/>
-        <v>347957.95703061519</v>
-      </c>
-      <c r="L33" s="9">
-        <f t="shared" si="8"/>
-        <v>0.23492132482340158</v>
-      </c>
-      <c r="M33" s="2">
-        <f t="shared" si="9"/>
         <v>323690.9700906311</v>
       </c>
       <c r="N33" s="34">
@@ -5838,7 +5838,7 @@
         <v>0.116061684650713</v>
       </c>
       <c r="O33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.35487739145755703</v>
       </c>
       <c r="P33" s="16">
@@ -5858,15 +5858,15 @@
         <v>0.20487739145755771</v>
       </c>
       <c r="U33">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V33" s="15">
+        <f t="shared" si="10"/>
+        <v>56751.238685451746</v>
+      </c>
+      <c r="W33" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V33" s="15">
-        <f t="shared" si="2"/>
-        <v>56751.238685451746</v>
-      </c>
-      <c r="W33" s="15">
-        <f t="shared" si="3"/>
         <v>127934.30080707553</v>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
         <v>633141.72843124997</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>128846.68316388392</v>
       </c>
       <c r="H34" s="4">
@@ -5901,23 +5901,23 @@
         <v>0.5</v>
       </c>
       <c r="I34" s="1">
+        <f t="shared" si="3"/>
+        <v>316570.86421562498</v>
+      </c>
+      <c r="J34" s="9">
+        <f t="shared" si="4"/>
+        <v>0.25115959241502306</v>
+      </c>
+      <c r="K34" s="2">
         <f t="shared" si="5"/>
-        <v>316570.86421562498</v>
-      </c>
-      <c r="J34" s="9">
+        <v>159019.61845373595</v>
+      </c>
+      <c r="L34" s="9">
         <f t="shared" si="6"/>
-        <v>0.25115959241502306</v>
-      </c>
-      <c r="K34" s="2">
+        <v>0.23354763147642457</v>
+      </c>
+      <c r="M34" s="2">
         <f t="shared" si="7"/>
-        <v>159019.61845373595</v>
-      </c>
-      <c r="L34" s="9">
-        <f t="shared" si="8"/>
-        <v>0.23354763147642457</v>
-      </c>
-      <c r="M34" s="2">
-        <f t="shared" si="9"/>
         <v>147868.75106400804</v>
       </c>
       <c r="N34" s="34">
@@ -5925,7 +5925,7 @@
         <v>4.0915365297205498E-2</v>
       </c>
       <c r="O34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.35350369811058002</v>
       </c>
       <c r="P34" s="16">
@@ -5945,15 +5945,15 @@
         <v>0.20350369811058039</v>
       </c>
       <c r="U34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="15">
+        <f t="shared" si="10"/>
+        <v>9157.5928745339097</v>
+      </c>
+      <c r="W34" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="15">
-        <f t="shared" si="2"/>
-        <v>9157.5928745339097</v>
-      </c>
-      <c r="W34" s="15">
-        <f t="shared" si="3"/>
         <v>20724.180082934938</v>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
         <v>73311050.902795792</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>27908244.928760629</v>
       </c>
       <c r="H35" s="4">
@@ -5988,23 +5988,23 @@
         <v>0.5</v>
       </c>
       <c r="I35" s="1">
+        <f t="shared" si="3"/>
+        <v>36655525.451397896</v>
+      </c>
+      <c r="J35" s="9">
+        <f t="shared" si="4"/>
+        <v>0.42833854153268414</v>
+      </c>
+      <c r="K35" s="2">
         <f t="shared" si="5"/>
-        <v>36655525.451397896</v>
-      </c>
-      <c r="J35" s="9">
+        <v>31401948.621931914</v>
+      </c>
+      <c r="L35" s="9">
         <f t="shared" si="6"/>
-        <v>0.42833854153268414</v>
-      </c>
-      <c r="K35" s="2">
+        <v>0.41072658059408562</v>
+      </c>
+      <c r="M35" s="2">
         <f t="shared" si="7"/>
-        <v>31401948.621931914</v>
-      </c>
-      <c r="L35" s="9">
-        <f t="shared" si="8"/>
-        <v>0.41072658059408562</v>
-      </c>
-      <c r="M35" s="2">
-        <f t="shared" si="9"/>
         <v>30110797.257064268</v>
       </c>
       <c r="N35" s="34">
@@ -6012,7 +6012,7 @@
         <v>7.3005110760756803E-2</v>
       </c>
       <c r="O35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.53068264722824099</v>
       </c>
       <c r="P35" s="16">
@@ -6032,15 +6032,15 @@
         <v>0.38068264722824102</v>
       </c>
       <c r="U35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="15">
+        <f t="shared" si="10"/>
+        <v>2840256.7208344121</v>
+      </c>
+      <c r="W35" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V35" s="15">
-        <f t="shared" si="2"/>
-        <v>2840256.7208344121</v>
-      </c>
-      <c r="W35" s="15">
-        <f t="shared" si="3"/>
         <v>4281665.11291687</v>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
         <v>163776.340062195</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>53006.622864105462</v>
       </c>
       <c r="H36" s="4">
@@ -6075,23 +6075,23 @@
         <v>0.5</v>
       </c>
       <c r="I36" s="1">
+        <f t="shared" si="3"/>
+        <v>81888.170031097499</v>
+      </c>
+      <c r="J36" s="9">
+        <f t="shared" si="4"/>
+        <v>0.37130840017907607</v>
+      </c>
+      <c r="K36" s="2">
         <f t="shared" si="5"/>
-        <v>81888.170031097499</v>
-      </c>
-      <c r="J36" s="9">
+        <v>60811.53081567795</v>
+      </c>
+      <c r="L36" s="9">
         <f t="shared" si="6"/>
-        <v>0.37130840017907607</v>
-      </c>
-      <c r="K36" s="2">
+        <v>0.35369643924047756</v>
+      </c>
+      <c r="M36" s="2">
         <f t="shared" si="7"/>
-        <v>60811.53081567795</v>
-      </c>
-      <c r="L36" s="9">
-        <f t="shared" si="8"/>
-        <v>0.35369643924047756</v>
-      </c>
-      <c r="M36" s="2">
-        <f t="shared" si="9"/>
         <v>57927.108311835946</v>
       </c>
       <c r="N36" s="34">
@@ -6099,7 +6099,7 @@
         <v>9.2897628793314799E-2</v>
       </c>
       <c r="O36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.47365250587463303</v>
       </c>
       <c r="P36" s="16">
@@ -6119,15 +6119,15 @@
         <v>0.32365250587463379</v>
       </c>
       <c r="U36">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V36" s="15">
+        <f t="shared" si="10"/>
+        <v>7206.3546210507247</v>
+      </c>
+      <c r="W36" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V36" s="15">
-        <f t="shared" si="2"/>
-        <v>7206.3546210507247</v>
-      </c>
-      <c r="W36" s="15">
-        <f t="shared" si="3"/>
         <v>12171.546915380386</v>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
         <v>2902430.34559192</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>787165.3225698485</v>
       </c>
       <c r="H37" s="4">
@@ -6162,23 +6162,23 @@
         <v>0.5</v>
       </c>
       <c r="I37" s="1">
+        <f t="shared" si="3"/>
+        <v>1451215.17279596</v>
+      </c>
+      <c r="J37" s="9">
+        <f t="shared" si="4"/>
+        <v>0.31886492564790314</v>
+      </c>
+      <c r="K37" s="2">
         <f t="shared" si="5"/>
-        <v>1451215.17279596</v>
-      </c>
-      <c r="J37" s="9">
+        <v>925483.23634538543</v>
+      </c>
+      <c r="L37" s="9">
         <f t="shared" si="6"/>
-        <v>0.31886492564790314</v>
-      </c>
-      <c r="K37" s="2">
+        <v>0.30125296470930463</v>
+      </c>
+      <c r="M37" s="2">
         <f t="shared" si="7"/>
-        <v>925483.23634538543</v>
-      </c>
-      <c r="L37" s="9">
-        <f t="shared" si="8"/>
-        <v>0.30125296470930463</v>
-      </c>
-      <c r="M37" s="2">
-        <f t="shared" si="9"/>
         <v>874365.74647181749</v>
       </c>
       <c r="N37" s="34">
@@ -6186,7 +6186,7 @@
         <v>9.2879304746987204E-2</v>
       </c>
       <c r="O37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.42120903134345999</v>
       </c>
       <c r="P37" s="16">
@@ -6206,15 +6206,15 @@
         <v>0.27120903134346008</v>
       </c>
       <c r="U37">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="15">
+        <f t="shared" si="10"/>
+        <v>113547.72476749575</v>
+      </c>
+      <c r="W37" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V37" s="15">
-        <f t="shared" si="2"/>
-        <v>113547.72476749575</v>
-      </c>
-      <c r="W37" s="15">
-        <f t="shared" si="3"/>
         <v>215660.57006010829</v>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
         <v>3083368.6624781401</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>308479.39463166182</v>
       </c>
       <c r="H38" s="4">
@@ -6249,23 +6249,23 @@
         <v>0.5</v>
       </c>
       <c r="I38" s="1">
+        <f t="shared" si="3"/>
+        <v>1541684.33123907</v>
+      </c>
+      <c r="J38" s="9">
+        <f t="shared" si="4"/>
+        <v>0.1477021191965821</v>
+      </c>
+      <c r="K38" s="2">
         <f t="shared" si="5"/>
-        <v>1541684.33123907</v>
-      </c>
-      <c r="J38" s="9">
+        <v>455420.08571235219</v>
+      </c>
+      <c r="L38" s="9">
         <f t="shared" si="6"/>
-        <v>0.1477021191965821</v>
-      </c>
-      <c r="K38" s="2">
+        <v>0.13009015825798359</v>
+      </c>
+      <c r="M38" s="2">
         <f t="shared" si="7"/>
-        <v>455420.08571235219</v>
-      </c>
-      <c r="L38" s="9">
-        <f t="shared" si="8"/>
-        <v>0.13009015825798359</v>
-      </c>
-      <c r="M38" s="2">
-        <f t="shared" si="9"/>
         <v>401115.91726948845</v>
       </c>
       <c r="N38" s="34">
@@ -6273,7 +6273,7 @@
         <v>1.52296060557599E-2</v>
       </c>
       <c r="O38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.25004622489213901</v>
       </c>
       <c r="P38" s="16">
@@ -6293,15 +6293,15 @@
         <v>0.10004622489213939</v>
       </c>
       <c r="U38">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="15">
+        <f t="shared" si="10"/>
+        <v>11741.793164692113</v>
+      </c>
+      <c r="W38" s="15">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V38" s="15">
-        <f t="shared" si="2"/>
-        <v>11741.793164692113</v>
-      </c>
-      <c r="W38" s="15">
-        <f t="shared" si="3"/>
         <v>37566.792043373913</v>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
         <v>1840578.2996984401</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>230912.94489712582</v>
       </c>
       <c r="H39" s="4">
@@ -6336,23 +6336,23 @@
         <v>0.5</v>
       </c>
       <c r="I39" s="1">
+        <f t="shared" si="3"/>
+        <v>920289.14984922006</v>
+      </c>
+      <c r="J39" s="9">
+        <f t="shared" si="4"/>
+        <v>0.17311262979619507</v>
+      </c>
+      <c r="K39" s="2">
         <f t="shared" si="5"/>
-        <v>920289.14984922006</v>
-      </c>
-      <c r="J39" s="9">
+        <v>318627.34980660625</v>
+      </c>
+      <c r="L39" s="9">
         <f t="shared" si="6"/>
-        <v>0.17311262979619507</v>
-      </c>
-      <c r="K39" s="2">
+        <v>0.15550066885759656</v>
+      </c>
+      <c r="M39" s="2">
         <f t="shared" si="7"/>
-        <v>318627.34980660625</v>
-      </c>
-      <c r="L39" s="9">
-        <f t="shared" si="8"/>
-        <v>0.15550066885759656</v>
-      </c>
-      <c r="M39" s="2">
-        <f t="shared" si="9"/>
         <v>286211.15668788523</v>
       </c>
       <c r="N39" s="34">
@@ -6360,7 +6360,7 @@
         <v>1.7267219640946602E-2</v>
       </c>
       <c r="O39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.27545673549175198</v>
       </c>
       <c r="P39" s="16">
@@ -6380,15 +6380,15 @@
         <v>0.1254567354917526</v>
       </c>
       <c r="U39">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V39" s="15">
+        <f t="shared" si="10"/>
+        <v>8754.4750025644225</v>
+      </c>
+      <c r="W39" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V39" s="15">
-        <f t="shared" si="2"/>
-        <v>8754.4750025644225</v>
-      </c>
-      <c r="W39" s="15">
-        <f t="shared" si="3"/>
         <v>25425.335813802405</v>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
         <v>140461.33305593001</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>20698.025806239526</v>
       </c>
       <c r="H40" s="4">
@@ -6423,23 +6423,23 @@
         <v>0.5</v>
       </c>
       <c r="I40" s="1">
+        <f t="shared" si="3"/>
+        <v>70230.666527965004</v>
+      </c>
+      <c r="J40" s="9">
+        <f t="shared" si="4"/>
+        <v>0.19501335814111209</v>
+      </c>
+      <c r="K40" s="2">
         <f t="shared" si="5"/>
-        <v>70230.666527965004</v>
-      </c>
-      <c r="J40" s="9">
+        <v>27391.836248214106</v>
+      </c>
+      <c r="L40" s="9">
         <f t="shared" si="6"/>
-        <v>0.19501335814111209</v>
-      </c>
-      <c r="K40" s="2">
+        <v>0.17740139720251358</v>
+      </c>
+      <c r="M40" s="2">
         <f t="shared" si="7"/>
-        <v>27391.836248214106</v>
-      </c>
-      <c r="L40" s="9">
-        <f t="shared" si="8"/>
-        <v>0.17740139720251358</v>
-      </c>
-      <c r="M40" s="2">
-        <f t="shared" si="9"/>
         <v>24918.036737049591</v>
       </c>
       <c r="N40" s="34">
@@ -6447,7 +6447,7 @@
         <v>5.83525301104015E-2</v>
       </c>
       <c r="O40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.297357463836669</v>
       </c>
       <c r="P40" s="16">
@@ -6467,15 +6467,15 @@
         <v>0.14735746383666989</v>
       </c>
       <c r="U40">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V40" s="15">
+        <f t="shared" si="10"/>
+        <v>2437.2232990584525</v>
+      </c>
+      <c r="W40" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V40" s="15">
-        <f t="shared" si="2"/>
-        <v>2437.2232990584525</v>
-      </c>
-      <c r="W40" s="15">
-        <f t="shared" si="3"/>
         <v>6557.0193331946321</v>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
         <v>2834744.0638050199</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>671244.7111064702</v>
       </c>
       <c r="H41" s="4">
@@ -6510,23 +6510,23 @@
         <v>0.5</v>
       </c>
       <c r="I41" s="1">
+        <f t="shared" si="3"/>
+        <v>1417372.03190251</v>
+      </c>
+      <c r="J41" s="9">
+        <f t="shared" si="4"/>
+        <v>0.28444789245240709</v>
+      </c>
+      <c r="K41" s="2">
         <f t="shared" si="5"/>
-        <v>1417372.03190251</v>
-      </c>
-      <c r="J41" s="9">
+        <v>806336.97459130979</v>
+      </c>
+      <c r="L41" s="9">
         <f t="shared" si="6"/>
-        <v>0.28444789245240709</v>
-      </c>
-      <c r="K41" s="2">
+        <v>0.26683593151380858</v>
+      </c>
+      <c r="M41" s="2">
         <f t="shared" si="7"/>
-        <v>806336.97459130979</v>
-      </c>
-      <c r="L41" s="9">
-        <f t="shared" si="8"/>
-        <v>0.26683593151380858</v>
-      </c>
-      <c r="M41" s="2">
-        <f t="shared" si="9"/>
         <v>756411.57286865171</v>
       </c>
       <c r="N41" s="34">
@@ -6534,7 +6534,7 @@
         <v>3.5372405873954897E-2</v>
       </c>
       <c r="O41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.386791998147964</v>
       </c>
       <c r="P41" s="16">
@@ -6554,15 +6554,15 @@
         <v>0.23679199814796451</v>
       </c>
       <c r="U41">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="V41" s="15">
+        <f t="shared" si="10"/>
+        <v>38784.297998057984</v>
+      </c>
+      <c r="W41" s="15">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="V41" s="15">
-        <f t="shared" si="2"/>
-        <v>38784.297998057984</v>
-      </c>
-      <c r="W41" s="15">
-        <f t="shared" si="3"/>
         <v>80217.374058956382</v>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
         <v>0.5</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2429544.3315206701</v>
       </c>
       <c r="J42" s="9">
@@ -6605,7 +6605,7 @@
         <v>0.1304338787447698</v>
       </c>
       <c r="K42" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>633789.78148521984</v>
       </c>
       <c r="L42" s="9">
@@ -6613,7 +6613,7 @@
         <v>0.11282191780617128</v>
       </c>
       <c r="M42" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>548211.7017545487</v>
       </c>
       <c r="N42" s="34">
@@ -6641,7 +6641,7 @@
         <v>8.2777984440326691E-2</v>
       </c>
       <c r="U42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V42" s="15">
@@ -6684,7 +6684,7 @@
         <v>0.65052527189254705</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>5697519.8553759847</v>
       </c>
       <c r="J43" s="9">
@@ -6692,7 +6692,7 @@
         <v>0.69818116619699011</v>
       </c>
       <c r="K43" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6114906.2594972886</v>
       </c>
       <c r="L43" s="9">
@@ -6700,7 +6700,7 @@
         <v>0.6805692052583916</v>
       </c>
       <c r="M43" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5960654.7623220244</v>
       </c>
       <c r="N43" s="34">
@@ -6728,7 +6728,7 @@
         <v>0.65052527189254761</v>
       </c>
       <c r="U43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V43" s="15">
@@ -6771,7 +6771,7 @@
         <v>0.5</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>416415.71491098747</v>
       </c>
       <c r="J44" s="9">
@@ -6779,7 +6779,7 @@
         <v>0.11764714017026488</v>
       </c>
       <c r="K44" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>97980.23596246801</v>
       </c>
       <c r="L44" s="9">
@@ -6787,7 +6787,7 @@
         <v>0.10003517923166637</v>
       </c>
       <c r="M44" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>83312.441352006237</v>
       </c>
       <c r="N44" s="34">
@@ -6815,7 +6815,7 @@
         <v>6.9991245865821838E-2</v>
       </c>
       <c r="U44">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V44" s="15">
@@ -6858,7 +6858,7 @@
         <v>0.5</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1569071.11298917</v>
       </c>
       <c r="J45" s="9">
@@ -6866,7 +6866,7 @@
         <v>0.17490847303979409</v>
       </c>
       <c r="K45" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>548887.6649275719</v>
       </c>
       <c r="L45" s="9">
@@ -6874,7 +6874,7 @@
         <v>0.15729651210119558</v>
       </c>
       <c r="M45" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>493618.82662387477</v>
       </c>
       <c r="N45" s="34">
@@ -6902,7 +6902,7 @@
         <v>0.12725257873535159</v>
       </c>
       <c r="U45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V45" s="15">
@@ -6945,7 +6945,7 @@
         <v>0.5</v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2947766.7797485897</v>
       </c>
       <c r="J46" s="9">
@@ -6953,7 +6953,7 @@
         <v>0.42156894400231903</v>
       </c>
       <c r="K46" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2485373.8570074593</v>
       </c>
       <c r="L46" s="9">
@@ -6961,7 +6961,7 @@
         <v>0.40395698306372052</v>
       </c>
       <c r="M46" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2381541.9502453981</v>
       </c>
       <c r="N46" s="34">
@@ -6989,7 +6989,7 @@
         <v>0.37391304969787598</v>
       </c>
       <c r="U46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V46" s="15">
@@ -7032,7 +7032,7 @@
         <v>0.5</v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>165298563.06571001</v>
       </c>
       <c r="J47" s="9">
@@ -7040,7 +7040,7 @@
         <v>0.23218977346532407</v>
       </c>
       <c r="K47" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>76761271.824741587</v>
       </c>
       <c r="L47" s="9">
@@ -7048,7 +7048,7 @@
         <v>0.21457781252672556</v>
       </c>
       <c r="M47" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>70938808.152902082</v>
       </c>
       <c r="N47" s="34">
@@ -7076,7 +7076,7 @@
         <v>0.18453387916088099</v>
       </c>
       <c r="U47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V47" s="15">
@@ -7119,7 +7119,7 @@
         <v>0.5</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>6341033.5861419849</v>
       </c>
       <c r="J48" s="9">
@@ -7127,7 +7127,7 @@
         <v>0.41734664037339708</v>
       </c>
       <c r="K48" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>5292818.1273424625</v>
       </c>
       <c r="L48" s="9">
@@ -7135,7 +7135,7 @@
         <v>0.39973467943479857</v>
       </c>
       <c r="M48" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5069462.055683515</v>
       </c>
       <c r="N48" s="34">
@@ -7163,7 +7163,7 @@
         <v>0.36969074606895452</v>
       </c>
       <c r="U48">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V48" s="15">
@@ -7206,7 +7206,7 @@
         <v>0.5</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>68693.5300995</v>
       </c>
       <c r="J49" s="9">
@@ -7214,7 +7214,7 @@
         <v>0.18020783259980708</v>
       </c>
       <c r="K49" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>24758.22434572101</v>
       </c>
       <c r="L49" s="9">
@@ -7222,7 +7222,7 @@
         <v>0.16259587166120856</v>
       </c>
       <c r="M49" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>22338.568808027339</v>
       </c>
       <c r="N49" s="34">
@@ -7250,7 +7250,7 @@
         <v>0.13255193829536441</v>
       </c>
       <c r="U49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V49" s="15">
@@ -7293,7 +7293,7 @@
         <v>0.5</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>600578.56974800257</v>
       </c>
       <c r="J50" s="9">
@@ -7301,7 +7301,7 @@
         <v>0.16048251732699909</v>
       </c>
       <c r="K50" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>192764.72145161629</v>
       </c>
       <c r="L50" s="9">
@@ -7309,7 +7309,7 @@
         <v>0.14287055638840057</v>
       </c>
       <c r="M50" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>171609.98882969393</v>
       </c>
       <c r="N50" s="34">
@@ -7337,7 +7337,7 @@
         <v>0.1128266230225563</v>
       </c>
       <c r="U50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V50" s="15">
@@ -7380,7 +7380,7 @@
         <v>0.55520486831664995</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>849494.58433222712</v>
       </c>
       <c r="J51" s="9">
@@ -7388,7 +7388,7 @@
         <v>0.602860762621093</v>
       </c>
       <c r="K51" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>922410.77515360236</v>
       </c>
       <c r="L51" s="9">
@@ -7396,7 +7396,7 @@
         <v>0.58524880168249449</v>
       </c>
       <c r="M51" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>895463.487241355</v>
       </c>
       <c r="N51" s="34">
@@ -7424,7 +7424,7 @@
         <v>0.55520486831665039</v>
       </c>
       <c r="U51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V51" s="15">
@@ -7467,7 +7467,7 @@
         <v>0.5</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>913401.63689664006</v>
       </c>
       <c r="J52" s="9">
@@ -7475,7 +7475,7 @@
         <v>0.28049994900338709</v>
       </c>
       <c r="K52" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>512418.22513823566</v>
       </c>
       <c r="L52" s="9">
@@ -7483,7 +7483,7 @@
         <v>0.26288798806478858</v>
       </c>
       <c r="M52" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>480244.63723768451</v>
       </c>
       <c r="N52" s="34">
@@ -7511,7 +7511,7 @@
         <v>0.23284405469894409</v>
       </c>
       <c r="U52">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V52" s="15">
@@ -7554,7 +7554,7 @@
         <v>0.5</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2047727.46411156</v>
       </c>
       <c r="J53" s="9">
@@ -7562,7 +7562,7 @@
         <v>0.41280929639451514</v>
       </c>
       <c r="K53" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1690641.8673352357</v>
       </c>
       <c r="L53" s="9">
@@ -7570,7 +7570,7 @@
         <v>0.39519733545591662</v>
       </c>
       <c r="M53" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1618512.8751135792</v>
       </c>
       <c r="N53" s="34">
@@ -7598,7 +7598,7 @@
         <v>0.36515340209007258</v>
       </c>
       <c r="U53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V53" s="15">
@@ -7641,7 +7641,7 @@
         <v>0.5</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>182657.01943104499</v>
       </c>
       <c r="J54" s="9">
@@ -7649,7 +7649,7 @@
         <v>0.42307715013139313</v>
       </c>
       <c r="K54" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>154556.02246476203</v>
       </c>
       <c r="L54" s="9">
@@ -7657,7 +7657,7 @@
         <v>0.40546518919279462</v>
       </c>
       <c r="M54" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>148122.12588200124</v>
       </c>
       <c r="N54" s="34">
@@ -7685,7 +7685,7 @@
         <v>0.37542125582695007</v>
       </c>
       <c r="U54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V54" s="15">
@@ -7728,7 +7728,7 @@
         <v>0.5</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2089457.62568552</v>
       </c>
       <c r="J55" s="9">
@@ -7736,7 +7736,7 @@
         <v>0.45797397091500813</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1913834.4117876845</v>
       </c>
       <c r="L55" s="9">
@@ -7744,7 +7744,7 @@
         <v>0.44036200997640962</v>
       </c>
       <c r="M55" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1840235.5196148243</v>
       </c>
       <c r="N55" s="34">
@@ -7772,7 +7772,7 @@
         <v>0.41031807661056519</v>
       </c>
       <c r="U55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V55" s="15">
@@ -7815,7 +7815,7 @@
         <v>0.5</v>
       </c>
       <c r="I56" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2907327.1231488897</v>
       </c>
       <c r="J56" s="9">
@@ -7823,7 +7823,7 @@
         <v>0.30366913869493006</v>
       </c>
       <c r="K56" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1765731.0467820645</v>
       </c>
       <c r="L56" s="9">
@@ -7831,7 +7831,7 @@
         <v>0.28605717775633155</v>
       </c>
       <c r="M56" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1663323.5833248119</v>
       </c>
       <c r="N56" s="34">
@@ -7859,7 +7859,7 @@
         <v>0.25601324439048773</v>
       </c>
       <c r="U56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V56" s="15">
@@ -7902,7 +7902,7 @@
         <v>0.5</v>
       </c>
       <c r="I57" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>8080997.5063170008</v>
       </c>
       <c r="J57" s="9">
@@ -7910,7 +7910,7 @@
         <v>0.17970071628205808</v>
       </c>
       <c r="K57" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2904322.0803173804</v>
       </c>
       <c r="L57" s="9">
@@ -7918,7 +7918,7 @@
         <v>0.16208875534345957</v>
       </c>
       <c r="M57" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2619677.6554650464</v>
       </c>
       <c r="N57" s="34">
@@ -7946,7 +7946,7 @@
         <v>0.13204482197761541</v>
       </c>
       <c r="U57">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V57" s="15">
@@ -7989,7 +7989,7 @@
         <v>0.5</v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>969502.65569188748</v>
       </c>
       <c r="J58" s="9">
@@ -7997,7 +7997,7 @@
         <v>0.17480732395761009</v>
       </c>
       <c r="K58" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>338952.32962259016</v>
       </c>
       <c r="L58" s="9">
@@ -8005,7 +8005,7 @@
         <v>0.15719536301901157</v>
       </c>
       <c r="M58" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>304802.64381876407</v>
       </c>
       <c r="N58" s="34">
@@ -8033,7 +8033,7 @@
         <v>0.1271514296531677</v>
       </c>
       <c r="U58">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V58" s="15">
@@ -8076,7 +8076,7 @@
         <v>0.5</v>
       </c>
       <c r="I59" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>114862.55274591999</v>
       </c>
       <c r="J59" s="9">
@@ -8084,7 +8084,7 @@
         <v>0.17854767933003909</v>
       </c>
       <c r="K59" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>41016.884469416451</v>
       </c>
       <c r="L59" s="9">
@@ -8092,7 +8092,7 @@
         <v>0.16093571839144058</v>
       </c>
       <c r="M59" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>36970.974884878742</v>
       </c>
       <c r="N59" s="34">
@@ -8120,7 +8120,7 @@
         <v>0.13089178502559659</v>
       </c>
       <c r="U59">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V59" s="15">
@@ -8163,7 +8163,7 @@
         <v>0.5</v>
       </c>
       <c r="I60" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>12376.50457734</v>
       </c>
       <c r="J60" s="9">
@@ -8171,7 +8171,7 @@
         <v>0.24892699613683208</v>
       </c>
       <c r="K60" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6161.6922142219973</v>
       </c>
       <c r="L60" s="9">
@@ -8179,7 +8179,7 @@
         <v>0.23131503519823357</v>
       </c>
       <c r="M60" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5725.7431838770017</v>
       </c>
       <c r="N60" s="34">
@@ -8207,7 +8207,7 @@
         <v>0.2012711018323898</v>
       </c>
       <c r="U60">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V60" s="15">
@@ -8250,7 +8250,7 @@
         <v>0.5</v>
       </c>
       <c r="I61" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1916861.1147829001</v>
       </c>
       <c r="J61" s="9">
@@ -8258,7 +8258,7 @@
         <v>0.28075943782441609</v>
       </c>
       <c r="K61" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1076353.6979478612</v>
       </c>
       <c r="L61" s="9">
@@ -8266,7 +8266,7 @@
         <v>0.26314747688581758</v>
       </c>
       <c r="M61" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1008834.3317913114</v>
       </c>
       <c r="N61" s="34">
@@ -8294,7 +8294,7 @@
         <v>0.23310354351997381</v>
       </c>
       <c r="U61">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V61" s="15">
@@ -8337,7 +8337,7 @@
         <v>0.5</v>
       </c>
       <c r="I62" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1773874.9707454024</v>
       </c>
       <c r="J62" s="9">
@@ -8345,7 +8345,7 @@
         <v>0.35055346682183808</v>
       </c>
       <c r="K62" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1243676.0414065749</v>
       </c>
       <c r="L62" s="9">
@@ -8353,7 +8353,7 @@
         <v>0.33294150588323956</v>
       </c>
       <c r="M62" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1181193.2080171236</v>
       </c>
       <c r="N62" s="34">
@@ -8381,7 +8381,7 @@
         <v>0.30289757251739502</v>
       </c>
       <c r="U62">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V62" s="15">
@@ -8424,7 +8424,7 @@
         <v>0.5</v>
       </c>
       <c r="I63" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>13198526.628068063</v>
       </c>
       <c r="J63" s="9">
@@ -8432,7 +8432,7 @@
         <v>0.24982158734910509</v>
       </c>
       <c r="K63" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6594553.7457867907</v>
       </c>
       <c r="L63" s="9">
@@ -8440,7 +8440,7 @@
         <v>0.23220962641050658</v>
       </c>
       <c r="M63" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6129649.8749456163</v>
       </c>
       <c r="N63" s="34">
@@ -8468,7 +8468,7 @@
         <v>0.2021656930446625</v>
       </c>
       <c r="U63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V63" s="15">
@@ -8511,7 +8511,7 @@
         <v>0.5</v>
       </c>
       <c r="I64" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>733254.79669053748</v>
       </c>
       <c r="J64" s="9">
@@ -8519,7 +8519,7 @@
         <v>0.47244961454980405</v>
       </c>
       <c r="K64" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>692851.89212647872</v>
       </c>
       <c r="L64" s="9">
@@ -8527,7 +8527,7 @@
         <v>0.45483765361120554</v>
       </c>
       <c r="M64" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>667023.7824517712</v>
       </c>
       <c r="N64" s="34">
@@ -8555,7 +8555,7 @@
         <v>0.42479372024536127</v>
       </c>
       <c r="U64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V64" s="15">
@@ -8598,7 +8598,7 @@
         <v>0.5</v>
       </c>
       <c r="I65" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>160502.20884202002</v>
       </c>
       <c r="J65" s="9">
@@ -8606,7 +8606,7 @@
         <v>0.1716130812417751</v>
       </c>
       <c r="K65" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>55088.557210979867</v>
       </c>
       <c r="L65" s="9">
@@ -8614,7 +8614,7 @@
         <v>0.15400112030317659</v>
       </c>
       <c r="M65" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>49435.039945610995</v>
       </c>
       <c r="N65" s="34">
@@ -8642,7 +8642,7 @@
         <v>0.12395718693733219</v>
       </c>
       <c r="U65">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V65" s="15">
@@ -8685,7 +8685,7 @@
         <v>0.5</v>
       </c>
       <c r="I66" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>195880.17543159999</v>
       </c>
       <c r="J66" s="9">
@@ -8693,7 +8693,7 @@
         <v>0.19908377423398507</v>
       </c>
       <c r="K66" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>77993.129245076081</v>
       </c>
       <c r="L66" s="9">
@@ -8701,7 +8701,7 @@
         <v>0.18147181329538656</v>
       </c>
       <c r="M66" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>71093.461248381762</v>
       </c>
       <c r="N66" s="34">
@@ -8729,7 +8729,7 @@
         <v>0.15142787992954251</v>
       </c>
       <c r="U66">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V66" s="15">
@@ -8772,7 +8772,7 @@
         <v>0.5</v>
       </c>
       <c r="I67" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>237886.94728774251</v>
       </c>
       <c r="J67" s="9">
@@ -8780,7 +8780,7 @@
         <v>0.22679687931649709</v>
       </c>
       <c r="K67" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>107904.03454997609</v>
       </c>
       <c r="L67" s="9">
@@ -8788,7 +8788,7 @@
         <v>0.20918491837789857</v>
       </c>
       <c r="M67" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>99524.723303107749</v>
       </c>
       <c r="N67" s="34">
@@ -8816,7 +8816,7 @@
         <v>0.17914098501205439</v>
       </c>
       <c r="U67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V67" s="15">
@@ -8859,7 +8859,7 @@
         <v>0.5</v>
       </c>
       <c r="I68" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>135387.46990977001</v>
       </c>
       <c r="J68" s="9">
@@ -8867,7 +8867,7 @@
         <v>0.18283344700448509</v>
       </c>
       <c r="K68" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>49506.715609638508</v>
       </c>
       <c r="L68" s="9">
@@ -8875,7 +8875,7 @@
         <v>0.16522148606588657</v>
       </c>
       <c r="M68" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>44737.837946385407</v>
       </c>
       <c r="N68" s="34">
@@ -8903,7 +8903,7 @@
         <v>0.1351775527000427</v>
       </c>
       <c r="U68">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="V68" s="15">
@@ -8946,7 +8946,7 @@
         <v>0.5</v>
       </c>
       <c r="I69" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>8760939.4692048822</v>
       </c>
       <c r="J69" s="9">
@@ -8954,7 +8954,7 @@
         <v>0.11836784973256659</v>
       </c>
       <c r="K69" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2074027.1332139103</v>
       </c>
       <c r="L69" s="9">
@@ -8962,7 +8962,7 @@
         <v>0.10075588879396807</v>
       </c>
       <c r="M69" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1765432.4857797856</v>
       </c>
       <c r="N69" s="34">
@@ -8990,7 +8990,7 @@
         <v>7.0711955428123474E-2</v>
       </c>
       <c r="U69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V69" s="15">
@@ -9033,7 +9033,7 @@
         <v>0.5</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>124178.11410582249</v>
       </c>
       <c r="J70" s="9">
@@ -9041,7 +9041,7 @@
         <v>0.18257787718885007</v>
       </c>
       <c r="K70" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>45344.352933511742</v>
       </c>
       <c r="L70" s="9">
@@ -9049,7 +9049,7 @@
         <v>0.16496591625025156</v>
       </c>
       <c r="M70" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>40970.31274339059</v>
       </c>
       <c r="N70" s="34">
@@ -9077,7 +9077,7 @@
         <v>0.13492198288440699</v>
       </c>
       <c r="U70">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V70" s="15">
@@ -9120,7 +9120,7 @@
         <v>0.5</v>
       </c>
       <c r="I71" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>982784.93033106497</v>
       </c>
       <c r="J71" s="9">
@@ -9128,7 +9128,7 @@
         <v>0.37359349324815305</v>
       </c>
       <c r="K71" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>734324.11046805058</v>
       </c>
       <c r="L71" s="9">
@@ -9136,7 +9136,7 @@
         <v>0.35598153230955454</v>
       </c>
       <c r="M71" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>699706.57085998263</v>
       </c>
       <c r="N71" s="34">
@@ -9164,7 +9164,7 @@
         <v>0.32593759894371033</v>
       </c>
       <c r="U71">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V71" s="15">
@@ -9207,7 +9207,7 @@
         <v>0.5</v>
       </c>
       <c r="I72" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>9733568.6250154544</v>
       </c>
       <c r="J72" s="9">
@@ -9215,7 +9215,7 @@
         <v>0.37457959249131711</v>
       </c>
       <c r="K72" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>7291992.3380891178</v>
       </c>
       <c r="L72" s="9">
@@ -9223,7 +9223,7 @@
         <v>0.3569676315527186</v>
       </c>
       <c r="M72" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6949137.8772552367</v>
       </c>
       <c r="N72" s="34">
@@ -9251,7 +9251,7 @@
         <v>0.32692369818687439</v>
       </c>
       <c r="U72">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V72" s="15">
@@ -9294,7 +9294,7 @@
         <v>0.5</v>
       </c>
       <c r="I73" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>241893.81483267</v>
       </c>
       <c r="J73" s="9">
@@ -9302,7 +9302,7 @@
         <v>0.1901234973918681</v>
       </c>
       <c r="K73" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>91979.396146896324</v>
       </c>
       <c r="L73" s="9">
@@ -9310,7 +9310,7 @@
         <v>0.17251153645326958</v>
       </c>
       <c r="M73" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>83458.94731065318</v>
       </c>
       <c r="N73" s="34">
@@ -9338,7 +9338,7 @@
         <v>0.1424676030874252</v>
       </c>
       <c r="U73">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V73" s="15">
@@ -9381,7 +9381,7 @@
         <v>0.5</v>
       </c>
       <c r="I74" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>234539.55926085499</v>
       </c>
       <c r="J74" s="9">
@@ -9389,7 +9389,7 @@
         <v>0.15587421401851209</v>
       </c>
       <c r="K74" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>73117.338912068022</v>
       </c>
       <c r="L74" s="9">
@@ -9397,7 +9397,7 @@
         <v>0.13826225307991358</v>
       </c>
       <c r="M74" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>64855.935799551444</v>
       </c>
       <c r="N74" s="34">
@@ -9425,7 +9425,7 @@
         <v>0.10821831971406939</v>
       </c>
       <c r="U74">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V74" s="15">
